--- a/escala_limpeza_27_09_2026.xlsx
+++ b/escala_limpeza_27_09_2026.xlsx
@@ -524,11 +524,15 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Lavanderia</t>
+          <t>Sala e copa</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -538,7 +542,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Área frontal da casa</t>
+          <t>Lavanderia</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -550,15 +554,11 @@
           <t>KOMIXÃO</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Sala e copa</t>
-        </is>
-      </c>
+      <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Garagem</t>
+          <t>Sala e copa</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Sala e copa</t>
+          <t>Área traseira da casa</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Geladeira</t>
+          <t>Área frontal da casa</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Cozinha</t>
+          <t>Geladeira</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -614,13 +614,13 @@
           <t>BAQUETADA</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -632,7 +632,7 @@
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Área traseira da casa</t>
+          <t>Garagem</t>
         </is>
       </c>
     </row>
